--- a/sample_students.xlsx
+++ b/sample_students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Students" sheetId="1" r:id="rId1"/>
+    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +418,12 @@
       <c r="F1" t="str">
         <v>year</v>
       </c>
+      <c r="G1" t="str">
+        <v>Interviewer Name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Interview Link</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -438,10 +444,198 @@
       <c r="F2" t="str">
         <v>1st Year</v>
       </c>
+      <c r="G2" t="str">
+        <v>Aayush Batra</v>
+      </c>
+      <c r="H2" t="str">
+        <v>https://meet.google.com/rx-tech-demo</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Priya Verma</v>
+      </c>
+      <c r="B3" t="str">
+        <v>24TIT015</v>
+      </c>
+      <c r="C3" t="str">
+        <v>priya.verma@tit.edu.in</v>
+      </c>
+      <c r="D3" t="str">
+        <v>9876543211</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Textile Technology</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1st Year</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Rohit Aggarwal</v>
+      </c>
+      <c r="H3" t="str">
+        <v>https://meet.google.com/rx-edit-demo</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Ananya Deshmukh</v>
+      </c>
+      <c r="B4" t="str">
+        <v>24TIT067</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ananya.deshmukh@tit.edu.in</v>
+      </c>
+      <c r="D4" t="str">
+        <v>9876543212</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Mechanical Engineering</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1st Year</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Manish Chawla</v>
+      </c>
+      <c r="H4" t="str">
+        <v>https://meet.google.com/rx-media-demo</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Rohan Gupta</v>
+      </c>
+      <c r="B5" t="str">
+        <v>24TIT088</v>
+      </c>
+      <c r="C5" t="str">
+        <v>rohan.gupta@tit.edu.in</v>
+      </c>
+      <c r="D5" t="str">
+        <v>9876543213</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Computer Science</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1st Year</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tanvi Mehra</v>
+      </c>
+      <c r="H5" t="str">
+        <v>https://meet.google.com/rx-ops-demo</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Sneha Patel</v>
+      </c>
+      <c r="B6" t="str">
+        <v>24TIT023</v>
+      </c>
+      <c r="C6" t="str">
+        <v>sneha.patel@tit.edu.in</v>
+      </c>
+      <c r="D6" t="str">
+        <v>9876543214</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2nd Year</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Simran Kaur</v>
+      </c>
+      <c r="H6" t="str">
+        <v>https://meet.google.com/rx-tech-demo</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Kunal Malhotra</v>
+      </c>
+      <c r="B7" t="str">
+        <v>24TIT045</v>
+      </c>
+      <c r="C7" t="str">
+        <v>kunal.malhotra@tit.edu.in</v>
+      </c>
+      <c r="D7" t="str">
+        <v>9876543215</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Electronics &amp; Comm.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1st Year</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Kavya Soni</v>
+      </c>
+      <c r="H7" t="str">
+        <v>https://meet.google.com/rx-edit-demo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Divya Saini</v>
+      </c>
+      <c r="B8" t="str">
+        <v>24TIT052</v>
+      </c>
+      <c r="C8" t="str">
+        <v>divya.saini@tit.edu.in</v>
+      </c>
+      <c r="D8" t="str">
+        <v>9876543216</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Fashion &amp; Apparel</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1st Year</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Deepak Yadav</v>
+      </c>
+      <c r="H8" t="str">
+        <v>https://meet.google.com/rx-media-demo</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Aditya Mehra</v>
+      </c>
+      <c r="B9" t="str">
+        <v>24TIT071</v>
+      </c>
+      <c r="C9" t="str">
+        <v>aditya.mehra@tit.edu.in</v>
+      </c>
+      <c r="D9" t="str">
+        <v>9876543217</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Textile Chemistry</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2nd Year</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Harshit Vashisht</v>
+      </c>
+      <c r="H9" t="str">
+        <v>https://meet.google.com/rx-ops-demo</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>